--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q720"/>
+  <dimension ref="A1:Q721"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28737,6 +28737,49 @@
       <c r="P720" t="inlineStr"/>
       <c r="Q720" t="inlineStr"/>
     </row>
+    <row r="721">
+      <c r="A721" s="2" t="n">
+        <v>46277</v>
+      </c>
+      <c r="B721" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C721" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D721" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E721" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F721" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G721" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H721" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I721" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J721" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K721" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L721" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M721" t="inlineStr"/>
+      <c r="N721" t="inlineStr"/>
+      <c r="O721" t="inlineStr"/>
+      <c r="P721" t="inlineStr"/>
+      <c r="Q721" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q721"/>
+  <dimension ref="A1:Q723"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28780,6 +28780,92 @@
       <c r="P721" t="inlineStr"/>
       <c r="Q721" t="inlineStr"/>
     </row>
+    <row r="722">
+      <c r="A722" s="2" t="n">
+        <v>46278</v>
+      </c>
+      <c r="B722" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C722" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D722" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E722" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F722" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G722" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H722" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I722" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J722" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K722" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L722" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M722" t="inlineStr"/>
+      <c r="N722" t="inlineStr"/>
+      <c r="O722" t="inlineStr"/>
+      <c r="P722" t="inlineStr"/>
+      <c r="Q722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" s="2" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B723" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C723" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D723" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E723" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F723" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G723" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H723" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I723" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J723" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K723" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L723" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M723" t="inlineStr"/>
+      <c r="N723" t="inlineStr"/>
+      <c r="O723" t="inlineStr"/>
+      <c r="P723" t="inlineStr"/>
+      <c r="Q723" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q723"/>
+  <dimension ref="A1:Q726"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28866,6 +28866,135 @@
       <c r="P723" t="inlineStr"/>
       <c r="Q723" t="inlineStr"/>
     </row>
+    <row r="724">
+      <c r="A724" s="2" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B724" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C724" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D724" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E724" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F724" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G724" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H724" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I724" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J724" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K724" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L724" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M724" t="inlineStr"/>
+      <c r="N724" t="inlineStr"/>
+      <c r="O724" t="inlineStr"/>
+      <c r="P724" t="inlineStr"/>
+      <c r="Q724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" s="2" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B725" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C725" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D725" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E725" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F725" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G725" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H725" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I725" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J725" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K725" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L725" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M725" t="inlineStr"/>
+      <c r="N725" t="inlineStr"/>
+      <c r="O725" t="inlineStr"/>
+      <c r="P725" t="inlineStr"/>
+      <c r="Q725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" s="2" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B726" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C726" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D726" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E726" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F726" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G726" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H726" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I726" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J726" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K726" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L726" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M726" t="inlineStr"/>
+      <c r="N726" t="inlineStr"/>
+      <c r="O726" t="inlineStr"/>
+      <c r="P726" t="inlineStr"/>
+      <c r="Q726" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q726"/>
+  <dimension ref="A1:Q728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28995,6 +28995,92 @@
       <c r="P726" t="inlineStr"/>
       <c r="Q726" t="inlineStr"/>
     </row>
+    <row r="727">
+      <c r="A727" s="2" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B727" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C727" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D727" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E727" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F727" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G727" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H727" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I727" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J727" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K727" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L727" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M727" t="inlineStr"/>
+      <c r="N727" t="inlineStr"/>
+      <c r="O727" t="inlineStr"/>
+      <c r="P727" t="inlineStr"/>
+      <c r="Q727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" s="2" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B728" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C728" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D728" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E728" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F728" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G728" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H728" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I728" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J728" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K728" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L728" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M728" t="inlineStr"/>
+      <c r="N728" t="inlineStr"/>
+      <c r="O728" t="inlineStr"/>
+      <c r="P728" t="inlineStr"/>
+      <c r="Q728" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q728"/>
+  <dimension ref="A1:Q730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29081,6 +29081,92 @@
       <c r="P728" t="inlineStr"/>
       <c r="Q728" t="inlineStr"/>
     </row>
+    <row r="729">
+      <c r="A729" s="2" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B729" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C729" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D729" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E729" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F729" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G729" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H729" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I729" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J729" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K729" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L729" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M729" t="inlineStr"/>
+      <c r="N729" t="inlineStr"/>
+      <c r="O729" t="inlineStr"/>
+      <c r="P729" t="inlineStr"/>
+      <c r="Q729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" s="2" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B730" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C730" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D730" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E730" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F730" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G730" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H730" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I730" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J730" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K730" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L730" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M730" t="inlineStr"/>
+      <c r="N730" t="inlineStr"/>
+      <c r="O730" t="inlineStr"/>
+      <c r="P730" t="inlineStr"/>
+      <c r="Q730" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q730"/>
+  <dimension ref="A1:Q732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29167,6 +29167,92 @@
       <c r="P730" t="inlineStr"/>
       <c r="Q730" t="inlineStr"/>
     </row>
+    <row r="731">
+      <c r="A731" s="2" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B731" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C731" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D731" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E731" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F731" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G731" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H731" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I731" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J731" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K731" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L731" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M731" t="inlineStr"/>
+      <c r="N731" t="inlineStr"/>
+      <c r="O731" t="inlineStr"/>
+      <c r="P731" t="inlineStr"/>
+      <c r="Q731" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" s="2" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B732" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C732" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D732" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E732" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F732" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G732" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H732" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I732" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J732" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K732" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L732" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M732" t="inlineStr"/>
+      <c r="N732" t="inlineStr"/>
+      <c r="O732" t="inlineStr"/>
+      <c r="P732" t="inlineStr"/>
+      <c r="Q732" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q732"/>
+  <dimension ref="A1:Q733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29253,6 +29253,49 @@
       <c r="P732" t="inlineStr"/>
       <c r="Q732" t="inlineStr"/>
     </row>
+    <row r="733">
+      <c r="A733" s="2" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B733" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C733" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D733" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E733" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F733" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G733" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H733" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I733" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J733" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K733" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L733" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M733" t="inlineStr"/>
+      <c r="N733" t="inlineStr"/>
+      <c r="O733" t="inlineStr"/>
+      <c r="P733" t="inlineStr"/>
+      <c r="Q733" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q733"/>
+  <dimension ref="A1:Q734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29296,6 +29296,49 @@
       <c r="P733" t="inlineStr"/>
       <c r="Q733" t="inlineStr"/>
     </row>
+    <row r="734">
+      <c r="A734" s="2" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B734" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C734" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D734" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E734" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F734" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G734" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H734" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I734" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J734" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K734" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L734" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M734" t="inlineStr"/>
+      <c r="N734" t="inlineStr"/>
+      <c r="O734" t="inlineStr"/>
+      <c r="P734" t="inlineStr"/>
+      <c r="Q734" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q738"/>
+  <dimension ref="A1:Q739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29511,6 +29511,49 @@
       <c r="P738" t="inlineStr"/>
       <c r="Q738" t="inlineStr"/>
     </row>
+    <row r="739">
+      <c r="A739" s="2" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B739" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C739" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D739" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E739" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F739" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G739" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H739" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I739" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J739" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K739" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L739" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M739" t="inlineStr"/>
+      <c r="N739" t="inlineStr"/>
+      <c r="O739" t="inlineStr"/>
+      <c r="P739" t="inlineStr"/>
+      <c r="Q739" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Quantities.xlsx
+++ b/Quantities.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q739"/>
+  <dimension ref="A1:Q741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29554,6 +29554,92 @@
       <c r="P739" t="inlineStr"/>
       <c r="Q739" t="inlineStr"/>
     </row>
+    <row r="740">
+      <c r="A740" s="2" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B740" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C740" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D740" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E740" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F740" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G740" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H740" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I740" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J740" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K740" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L740" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M740" t="inlineStr"/>
+      <c r="N740" t="inlineStr"/>
+      <c r="O740" t="inlineStr"/>
+      <c r="P740" t="inlineStr"/>
+      <c r="Q740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" s="2" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B741" t="n">
+        <v>0.00045565</v>
+      </c>
+      <c r="C741" t="n">
+        <v>1.21e-05</v>
+      </c>
+      <c r="D741" t="n">
+        <v>7.45e-06</v>
+      </c>
+      <c r="E741" t="n">
+        <v>3.635e-05</v>
+      </c>
+      <c r="F741" t="n">
+        <v>0.0003977</v>
+      </c>
+      <c r="G741" t="n">
+        <v>1863.22125016</v>
+      </c>
+      <c r="H741" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="I741" t="n">
+        <v>0.0004431</v>
+      </c>
+      <c r="J741" t="n">
+        <v>4663.85449423</v>
+      </c>
+      <c r="K741" t="n">
+        <v>0.83831888</v>
+      </c>
+      <c r="L741" t="n">
+        <v>0.14694965</v>
+      </c>
+      <c r="M741" t="inlineStr"/>
+      <c r="N741" t="inlineStr"/>
+      <c r="O741" t="inlineStr"/>
+      <c r="P741" t="inlineStr"/>
+      <c r="Q741" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
